--- a/DIM_LIMSv2.xlsx
+++ b/DIM_LIMSv2.xlsx
@@ -107,12 +107,6 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00C2410C"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <color rgb="002C3E50"/>
       <sz val="9"/>
     </font>
@@ -153,19 +147,25 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0015803D"/>
+      <color rgb="00B45309"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0014532D"/>
+      <color rgb="00166534"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C2410C"/>
       <sz val="9"/>
     </font>
     <font>
@@ -190,7 +190,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001D4ED8"/>
+        <fgColor rgb="00EA580C"/>
       </patternFill>
     </fill>
     <fill>
@@ -290,16 +290,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -308,19 +305,19 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -329,48 +326,51 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -757,14 +757,14 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>System: LIMSv2   |   Source: AT auto-feed (2 periods)   |   Period 1: 01-Jan-2025 → 30-Mar-2025   |   Period 2: 01-Apr-2025 → 27-Jun-2025   |   Generated: 2026-04-13 03:28 UTC</t>
+          <t>System: FillV2   |   Source: AT auto-feed (2 periods)   |   Period 1: 01-Jan-2025 → 30-Mar-2025   |   Period 2: 01-Apr-2025 → 27-Jun-2025   |   Generated: 2026-04-13 04:19 UTC</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>DI Posture — 01-Apr-2025 → 27-Jun-2025: STABLE</t>
+          <t>DI Posture — 01-Apr-2025 → 27-Jun-2025: DETERIORATING</t>
         </is>
       </c>
     </row>
@@ -882,26 +882,6 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Dormant Account Flags</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>+16.7%</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>Moderate Increase</t>
-        </is>
-      </c>
-    </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
@@ -910,14 +890,14 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>11 user(s) flagged High/Critical in 2 or more periods.  Most persistent: analyst_a.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Regulatory Basis: ALCOA+ | 21 CFR Part 11 §11.10(e) | EU Annex 11 Clause 9 | FDA CSA Final Guidance (Sep 2021)</t>
         </is>
@@ -958,7 +938,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Period-over-Period Trend Analysis</t>
         </is>
@@ -1042,126 +1022,126 @@
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>01-Jan-2025 → 30-Mar-2025</t>
         </is>
       </c>
-      <c r="B3" s="19" t="n">
+      <c r="B3" s="18" t="n">
         <v>420</v>
       </c>
-      <c r="C3" s="19" t="n">
+      <c r="C3" s="18" t="n">
         <v>420</v>
       </c>
-      <c r="D3" s="19" t="n">
+      <c r="D3" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="E3" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="H3" s="19" t="n">
+      <c r="G3" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="18" t="n">
         <v>3.28</v>
       </c>
-      <c r="I3" s="20" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K3" s="21" t="inlineStr">
+      <c r="K3" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M3" s="21" t="inlineStr">
+      <c r="M3" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O3" s="21" t="inlineStr">
+      <c r="O3" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>01-Apr-2025 → 27-Jun-2025</t>
         </is>
       </c>
-      <c r="B4" s="23" t="n">
+      <c r="B4" s="22" t="n">
         <v>418</v>
       </c>
-      <c r="C4" s="23" t="n">
+      <c r="C4" s="22" t="n">
         <v>418</v>
       </c>
-      <c r="D4" s="23" t="n">
+      <c r="D4" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="E4" s="23" t="n">
+      <c r="E4" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="23" t="n">
+      <c r="F4" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="23" t="n">
-        <v>28</v>
-      </c>
-      <c r="H4" s="23" t="n">
+      <c r="G4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="22" t="n">
         <v>3.28</v>
       </c>
-      <c r="I4" s="24" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
+        <is>
+          <t>Deteriorating</t>
+        </is>
+      </c>
+      <c r="J4" s="24" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="J4" s="25" t="inlineStr">
+      <c r="L4" s="24" t="inlineStr">
         <is>
           <t>-0.5%</t>
         </is>
       </c>
-      <c r="K4" s="26" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="L4" s="25" t="inlineStr">
-        <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="M4" s="26" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
-      </c>
-      <c r="N4" s="27" t="inlineStr">
+      <c r="N4" s="26" t="inlineStr">
         <is>
           <t>+75.0%</t>
         </is>
       </c>
-      <c r="O4" s="27" t="inlineStr">
+      <c r="O4" s="26" t="inlineStr">
         <is>
           <t>Significant Increase</t>
         </is>
@@ -1191,7 +1171,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Repeat High-Risk Users — Flagged High/Critical in 2+ Periods</t>
         </is>
@@ -1235,363 +1215,363 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>analyst_a</t>
         </is>
       </c>
-      <c r="B3" s="29" t="n">
+      <c r="B3" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="30" t="inlineStr">
-        <is>
-          <t>01-Apr-2025 → 27-Jun-2025, 01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="D3" s="29" t="inlineStr">
-        <is>
-          <t>01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="E3" s="29" t="n">
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 → 30-Mar-2025, 01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="n">
         <v>139</v>
       </c>
-      <c r="F3" s="30" t="inlineStr">
+      <c r="F3" s="29" t="inlineStr">
         <is>
           <t>Rule 1 — Vague Rationale [HIGH]</t>
         </is>
       </c>
-      <c r="G3" s="29" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t>Critical, High</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>analyst_b</t>
         </is>
       </c>
-      <c r="B4" s="29" t="n">
+      <c r="B4" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="30" t="inlineStr">
-        <is>
-          <t>01-Apr-2025 → 27-Jun-2025, 01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="D4" s="29" t="inlineStr">
-        <is>
-          <t>01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="E4" s="29" t="n">
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 → 30-Mar-2025, 01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="D4" s="28" t="inlineStr">
+        <is>
+          <t>01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="E4" s="28" t="n">
         <v>132</v>
       </c>
-      <c r="F4" s="30" t="inlineStr">
+      <c r="F4" s="29" t="inlineStr">
         <is>
           <t>Rule 1 — Vague Rationale [HIGH]</t>
         </is>
       </c>
-      <c r="G4" s="29" t="inlineStr">
+      <c r="G4" s="28" t="inlineStr">
         <is>
           <t>Critical, High</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>analyst_e</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="30" t="inlineStr">
-        <is>
-          <t>01-Apr-2025 → 27-Jun-2025, 01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="D5" s="29" t="inlineStr">
-        <is>
-          <t>01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="E5" s="29" t="n">
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 → 30-Mar-2025, 01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="n">
         <v>121</v>
       </c>
-      <c r="F5" s="30" t="inlineStr">
+      <c r="F5" s="29" t="inlineStr">
         <is>
           <t>Rule 1 — Vague Rationale [HIGH]</t>
         </is>
       </c>
-      <c r="G5" s="29" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>Critical, High</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>analyst_c</t>
         </is>
       </c>
-      <c r="B6" s="29" t="n">
+      <c r="B6" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="30" t="inlineStr">
-        <is>
-          <t>01-Apr-2025 → 27-Jun-2025, 01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="D6" s="29" t="inlineStr">
-        <is>
-          <t>01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="E6" s="29" t="n">
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 → 30-Mar-2025, 01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="n">
         <v>114</v>
       </c>
-      <c r="F6" s="30" t="inlineStr">
+      <c r="F6" s="29" t="inlineStr">
         <is>
           <t>Rule 1 — Vague Rationale [HIGH]</t>
         </is>
       </c>
-      <c r="G6" s="29" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>Critical, High</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>analyst_d</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="30" t="inlineStr">
-        <is>
-          <t>01-Apr-2025 → 27-Jun-2025, 01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="D7" s="29" t="inlineStr">
-        <is>
-          <t>01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="E7" s="29" t="n">
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 → 30-Mar-2025, 01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="n">
         <v>103</v>
       </c>
-      <c r="F7" s="30" t="inlineStr">
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>Rule 1 — Vague Rationale [HIGH]</t>
         </is>
       </c>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="G7" s="28" t="inlineStr">
         <is>
           <t>Critical, High</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>admin_sys</t>
         </is>
       </c>
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="30" t="inlineStr">
-        <is>
-          <t>01-Apr-2025 → 27-Jun-2025, 01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="D8" s="29" t="inlineStr">
-        <is>
-          <t>01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="E8" s="29" t="n">
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 → 30-Mar-2025, 01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="n">
         <v>69</v>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F8" s="29" t="inlineStr">
         <is>
           <t>Rule 3 — Admin/GxP Conflict [CRITICAL]</t>
         </is>
       </c>
-      <c r="G8" s="29" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>Critical, High</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>admin_qc</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="30" t="inlineStr">
-        <is>
-          <t>01-Apr-2025 → 27-Jun-2025, 01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="D9" s="29" t="inlineStr">
-        <is>
-          <t>01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="E9" s="29" t="n">
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 → 30-Mar-2025, 01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="n">
         <v>58</v>
       </c>
-      <c r="F9" s="30" t="inlineStr">
+      <c r="F9" s="29" t="inlineStr">
         <is>
           <t>Rule 3 — Admin/GxP Conflict [CRITICAL]</t>
         </is>
       </c>
-      <c r="G9" s="29" t="inlineStr">
+      <c r="G9" s="28" t="inlineStr">
         <is>
           <t>Critical, High</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>analyst_z</t>
         </is>
       </c>
-      <c r="B10" s="29" t="n">
+      <c r="B10" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="30" t="inlineStr">
-        <is>
-          <t>01-Apr-2025 → 27-Jun-2025, 01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="D10" s="29" t="inlineStr">
-        <is>
-          <t>01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="E10" s="29" t="n">
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 → 30-Mar-2025, 01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="n">
         <v>27</v>
       </c>
-      <c r="F10" s="30" t="inlineStr">
+      <c r="F10" s="29" t="inlineStr">
         <is>
           <t>Rule 1 — Vague Rationale [HIGH]</t>
         </is>
       </c>
-      <c r="G10" s="29" t="inlineStr">
+      <c r="G10" s="28" t="inlineStr">
         <is>
           <t>Critical, High</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>analyst_new</t>
         </is>
       </c>
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="30" t="inlineStr">
-        <is>
-          <t>01-Apr-2025 → 27-Jun-2025, 01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="D11" s="29" t="inlineStr">
-        <is>
-          <t>01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="E11" s="29" t="n">
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 → 30-Mar-2025, 01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="n">
         <v>22</v>
       </c>
-      <c r="F11" s="30" t="inlineStr">
+      <c r="F11" s="29" t="inlineStr">
         <is>
           <t>Rule 6 — Record Reconstruction Pattern [CRITICAL]</t>
         </is>
       </c>
-      <c r="G11" s="29" t="inlineStr">
+      <c r="G11" s="28" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>dba_prod</t>
         </is>
       </c>
-      <c r="B12" s="29" t="n">
+      <c r="B12" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="30" t="inlineStr">
-        <is>
-          <t>01-Apr-2025 → 27-Jun-2025, 01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="D12" s="29" t="inlineStr">
-        <is>
-          <t>01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="E12" s="29" t="n">
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 → 30-Mar-2025, 01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="n">
         <v>21</v>
       </c>
-      <c r="F12" s="30" t="inlineStr">
+      <c r="F12" s="29" t="inlineStr">
         <is>
           <t>Rule 3 — Admin/GxP Conflict [CRITICAL]</t>
         </is>
       </c>
-      <c r="G12" s="29" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>svc_lims_batch</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="30" t="inlineStr">
-        <is>
-          <t>01-Apr-2025 → 27-Jun-2025, 01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="D13" s="29" t="inlineStr">
-        <is>
-          <t>01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="E13" s="29" t="n">
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 → 30-Mar-2025, 01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="n">
         <v>21</v>
       </c>
-      <c r="F13" s="30" t="inlineStr">
+      <c r="F13" s="29" t="inlineStr">
         <is>
           <t>Rule 1 — Vague Rationale [HIGH]</t>
         </is>
       </c>
-      <c r="G13" s="29" t="inlineStr">
+      <c r="G13" s="28" t="inlineStr">
         <is>
           <t>Critical, High</t>
         </is>
@@ -1623,14 +1603,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Rule Recurrence Analysis — Rules Firing Across Multiple Periods</t>
         </is>
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="31" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>Rules recurring across periods indicate systemic control gaps rather than isolated incidents. Prioritise for CAPA.</t>
         </is>
@@ -1684,224 +1664,224 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Rule 1</t>
         </is>
       </c>
-      <c r="B4" s="33" t="n">
+      <c r="B4" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="34" t="inlineStr">
-        <is>
-          <t>01-Apr-2025 → 27-Jun-2025, 01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="D4" s="33" t="n">
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 → 30-Mar-2025, 01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="n">
         <v>628</v>
       </c>
-      <c r="E4" s="33" t="n">
+      <c r="E4" s="32" t="n">
+        <v>297</v>
+      </c>
+      <c r="F4" s="32" t="n">
         <v>331</v>
       </c>
-      <c r="F4" s="33" t="n">
-        <v>297</v>
-      </c>
-      <c r="G4" s="33" t="inlineStr">
-        <is>
-          <t>-10.3%</t>
-        </is>
-      </c>
-      <c r="H4" s="35" t="inlineStr">
-        <is>
-          <t>Slight Decrease</t>
-        </is>
-      </c>
-      <c r="I4" s="33" t="n">
+      <c r="G4" s="32" t="inlineStr">
+        <is>
+          <t>+11.4%</t>
+        </is>
+      </c>
+      <c r="H4" s="34" t="inlineStr">
+        <is>
+          <t>Slight Increase</t>
+        </is>
+      </c>
+      <c r="I4" s="32" t="n">
         <v>628</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>Rule 3</t>
         </is>
       </c>
-      <c r="B5" s="37" t="n">
+      <c r="B5" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="38" t="inlineStr">
-        <is>
-          <t>01-Apr-2025 → 27-Jun-2025, 01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="D5" s="37" t="n">
+      <c r="C5" s="37" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 → 30-Mar-2025, 01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="n">
         <v>101</v>
       </c>
-      <c r="E5" s="37" t="n">
+      <c r="E5" s="36" t="n">
+        <v>56</v>
+      </c>
+      <c r="F5" s="36" t="n">
         <v>45</v>
       </c>
-      <c r="F5" s="37" t="n">
-        <v>56</v>
-      </c>
-      <c r="G5" s="37" t="inlineStr">
-        <is>
-          <t>+24.4%</t>
-        </is>
-      </c>
-      <c r="H5" s="39" t="inlineStr">
+      <c r="G5" s="36" t="inlineStr">
+        <is>
+          <t>-19.6%</t>
+        </is>
+      </c>
+      <c r="H5" s="38" t="inlineStr">
+        <is>
+          <t>Moderate Decrease</t>
+        </is>
+      </c>
+      <c r="I5" s="36" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>Rule 6</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 → 30-Mar-2025, 01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="n">
+        <v>22</v>
+      </c>
+      <c r="E6" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" s="32" t="inlineStr">
+        <is>
+          <t>+75.0%</t>
+        </is>
+      </c>
+      <c r="H6" s="39" t="inlineStr">
+        <is>
+          <t>Significant Increase</t>
+        </is>
+      </c>
+      <c r="I6" s="32" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>Rule 8</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 → 30-Mar-2025</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="n">
+        <v>16</v>
+      </c>
+      <c r="E7" s="36" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" s="36" t="n">
+        <v>16</v>
+      </c>
+      <c r="G7" s="36" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+      <c r="H7" s="40" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="I7" s="36" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>Rule 9</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>01-Jan-2025 → 30-Mar-2025, 01-Apr-2025 → 27-Jun-2025</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="n">
+        <v>52</v>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="F8" s="32" t="n">
+        <v>28</v>
+      </c>
+      <c r="G8" s="32" t="inlineStr">
+        <is>
+          <t>+16.7%</t>
+        </is>
+      </c>
+      <c r="H8" s="41" t="inlineStr">
         <is>
           <t>Moderate Increase</t>
         </is>
       </c>
-      <c r="I5" s="37" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="32" t="inlineStr">
-        <is>
-          <t>Rule 6</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="34" t="inlineStr">
-        <is>
-          <t>01-Apr-2025 → 27-Jun-2025, 01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="D6" s="33" t="n">
-        <v>22</v>
-      </c>
-      <c r="E6" s="33" t="n">
-        <v>14</v>
-      </c>
-      <c r="F6" s="33" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" s="33" t="inlineStr">
-        <is>
-          <t>-42.9%</t>
-        </is>
-      </c>
-      <c r="H6" s="40" t="inlineStr">
-        <is>
-          <t>Significant Decrease</t>
-        </is>
-      </c>
-      <c r="I6" s="33" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="36" t="inlineStr">
-        <is>
-          <t>Rule 8</t>
-        </is>
-      </c>
-      <c r="B7" s="37" t="n">
+      <c r="I8" s="32" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>Rule 12</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="38" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>01-Jan-2025 → 30-Mar-2025</t>
         </is>
       </c>
-      <c r="D7" s="37" t="n">
-        <v>16</v>
-      </c>
-      <c r="E7" s="37" t="n">
-        <v>16</v>
-      </c>
-      <c r="F7" s="37" t="n">
-        <v>16</v>
-      </c>
-      <c r="G7" s="37" t="inlineStr">
+      <c r="D9" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="E9" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="F9" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="G9" s="36" t="inlineStr">
         <is>
           <t>+0.0%</t>
         </is>
       </c>
-      <c r="H7" s="41" t="inlineStr">
+      <c r="H9" s="40" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="I7" s="37" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="32" t="inlineStr">
-        <is>
-          <t>Rule 9</t>
-        </is>
-      </c>
-      <c r="B8" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="34" t="inlineStr">
-        <is>
-          <t>01-Apr-2025 → 27-Jun-2025, 01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="D8" s="33" t="n">
-        <v>52</v>
-      </c>
-      <c r="E8" s="33" t="n">
-        <v>28</v>
-      </c>
-      <c r="F8" s="33" t="n">
-        <v>24</v>
-      </c>
-      <c r="G8" s="33" t="inlineStr">
-        <is>
-          <t>-14.3%</t>
-        </is>
-      </c>
-      <c r="H8" s="35" t="inlineStr">
-        <is>
-          <t>Slight Decrease</t>
-        </is>
-      </c>
-      <c r="I8" s="33" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="36" t="inlineStr">
-        <is>
-          <t>Rule 12</t>
-        </is>
-      </c>
-      <c r="B9" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="38" t="inlineStr">
-        <is>
-          <t>01-Jan-2025 → 30-Mar-2025</t>
-        </is>
-      </c>
-      <c r="D9" s="37" t="n">
-        <v>19</v>
-      </c>
-      <c r="E9" s="37" t="n">
-        <v>19</v>
-      </c>
-      <c r="F9" s="37" t="n">
-        <v>19</v>
-      </c>
-      <c r="G9" s="37" t="inlineStr">
-        <is>
-          <t>+0.0%</t>
-        </is>
-      </c>
-      <c r="H9" s="41" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
-      </c>
-      <c r="I9" s="37" t="n">
+      <c r="I9" s="36" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1916,7 +1896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="105" customWidth="1" min="1" max="1"/>
@@ -1930,7 +1910,7 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="31" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>This narrative is generated from calculated metrics only. Every statement cites a specific count or percentage derived from the uploaded data. Human reviewer confirmation required before use as regulatory evidence.</t>
         </is>
@@ -1956,7 +1936,7 @@
     <row r="7" ht="14" customHeight="1">
       <c r="A7" s="44" t="inlineStr">
         <is>
-          <t>This report covers 2 review periods from 01-Jan-2025 → 30-Mar-2025 to 01-Apr-2025 → 27-Jun-2025. Total findings moved from 420 in 01-Jan-2025 → 30-Mar-2025 to 418 in 01-Apr-2025 → 27-Jun-2025 (-0.5% overall change). DI Posture in the latest period: STABLE.</t>
+          <t>This report covers 2 review periods from 01-Jan-2025 → 30-Mar-2025 to 01-Apr-2025 → 27-Jun-2025. Total findings moved from 420 in 01-Jan-2025 → 30-Mar-2025 to 418 in 01-Apr-2025 → 27-Jun-2025 (-0.5% overall change). DI Posture in the latest period: DETERIORATING.</t>
         </is>
       </c>
     </row>
@@ -2029,24 +2009,17 @@
       </c>
     </row>
     <row r="20" ht="14" customHeight="1">
-      <c r="A20" s="44" t="inlineStr">
-        <is>
-          <t>2. Dormant Account Flags: 28 findings in latest period (+16.7% vs prior period — Moderate Increase).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="14" customHeight="1">
-      <c r="A21" s="44" t="inlineStr"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A20" s="44" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="43" t="inlineStr">
         <is>
           <t>## Reviewer Statement</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="44" t="inlineStr">
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="44" t="inlineStr">
         <is>
           <t>This summary was generated from calculated metrics. All counts and percentages are derived deterministically from the uploaded data. Narrative text does not influence risk classification. Human reviewer confirmation is required before this document is used as regulatory evidence.</t>
         </is>
